--- a/template.xlsx
+++ b/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connorgp1-my.sharepoint.com/personal/q_hoang_connorgp_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{3867A7FF-80A7-4AE0-9F4C-14D1C1FB01D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16417667-2725-41C6-A7FC-E0CD1DFF1DE3}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="13_ncr:1_{3867A7FF-80A7-4AE0-9F4C-14D1C1FB01D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57254762-4778-407D-BE10-9768CBF4F270}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="0" windowWidth="21720" windowHeight="13470" activeTab="1" xr2:uid="{E7FE2CFA-5EB4-4D3E-8BCC-3D04D8E6801F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17010" windowHeight="9225" xr2:uid="{E7FE2CFA-5EB4-4D3E-8BCC-3D04D8E6801F}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>Client : Engagement</t>
   </si>
@@ -67,15 +67,6 @@
     <t>Purpose</t>
   </si>
   <si>
-    <t>Github Link</t>
-  </si>
-  <si>
-    <t>To help professionals at CG with their weekly timesheet data input</t>
-  </si>
-  <si>
-    <t>Created by</t>
-  </si>
-  <si>
     <t>Date created</t>
   </si>
   <si>
@@ -85,9 +76,6 @@
     <t>Q Hoang (q.hoang@connorgp.com)</t>
   </si>
   <si>
-    <t>Special thanks to Nam for helping me test the solution</t>
-  </si>
-  <si>
     <t>Sun</t>
   </si>
   <si>
@@ -112,13 +100,23 @@
     <t>Timesheet template v1.2</t>
   </si>
   <si>
-    <t>https://github.com/hoangcodes/netsuitesuiteprojectspro-extension</t>
+    <t>❌ DO NOT add columns</t>
+  </si>
+  <si>
+    <t>❌ DO NOT delete columns</t>
+  </si>
+  <si>
+    <t>✅ OK to add rows</t>
+  </si>
+  <si>
+    <t>✅ OK to delete rows (but you don't need too)</t>
+  </si>
+  <si>
+    <t>✅ For Client : Engagement and Task, the more precise to OpenAir the better</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Please use the template like how you would normally. Make a copy of Template tab or your latest tab (because often you work with the same clients from the week before). 
-Add rows if needed. No need to delete rows when saving file as CSV. The code on the backend mainly relies on the "Total Time" row to know when to stop parsing the rows, and it won't read any column data past column Q. 
-</t>
+      <t xml:space="preserve">✅ OK to make multiline comments with </t>
     </r>
     <r>
       <rPr>
@@ -129,7 +127,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Add columns</t>
+      <t>Alt+Enter</t>
     </r>
     <r>
       <rPr>
@@ -139,118 +137,20 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: no
-</t>
+      <t xml:space="preserve"> in the same cell</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Delete columns</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: no
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add rows</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: yes works as expected
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Delete rows</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: optional, you don't need too
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Saturday and sunday columns</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: use as normal, greyed out because for some people, the week starting on Sunday is unfamiliar and misinput of data is a common accident
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Notes cells</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: For multi-line notes, use Alt+Enter to create a new line in the same cell</t>
-    </r>
+  </si>
+  <si>
+    <t>✅ OK to make copy from sheet</t>
+  </si>
+  <si>
+    <t>Developer</t>
+  </si>
+  <si>
+    <t>To help professionals that use the Netsuite's SuiteProjects Pro application with their weekly timesheet data input</t>
+  </si>
+  <si>
+    <t>Special thanks to Nam for helping me test the solution</t>
   </si>
 </sst>
 </file>
@@ -263,7 +163,7 @@
     <numFmt numFmtId="165" formatCode="ddd\,\ mmm\ d"/>
     <numFmt numFmtId="166" formatCode="mmmm\ yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,14 +201,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -431,54 +323,49 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -533,10 +420,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="1" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -549,35 +458,9 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="1" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="3">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{CE8C5FC9-2EAD-448C-B85F-0C3FE57C7FCC}"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{629D5829-13F4-4135-B16A-322FDEE14277}"/>
   </cellStyles>
@@ -978,16 +861,38 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{A105A4D7-796A-4408-86EC-03EFDE02F9FA}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;93d9a662-c101-47bf-b5d3-8110819e0849&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DFBA673-930E-41EB-BF51-58523BE880E5}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="60" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.85546875" customWidth="1"/>
     <col min="3" max="3" width="2.7109375" customWidth="1"/>
     <col min="4" max="4" width="255.7109375" customWidth="1"/>
   </cols>
@@ -996,65 +901,86 @@
       <c r="A1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="37" t="s">
-        <v>21</v>
+      <c r="B1" s="31" t="s">
+        <v>17</v>
       </c>
       <c r="C1" s="23"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="31" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>12</v>
       </c>
       <c r="C2" s="23"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="38">
+        <v>7</v>
+      </c>
+      <c r="B3" s="32">
         <v>46204</v>
       </c>
-      <c r="C3" s="29"/>
+      <c r="C3" s="25"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="39" t="s">
+      <c r="B8" s="33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="29"/>
+      <c r="B9" s="34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
+      <c r="B10" s="34" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="29"/>
+      <c r="B11" s="34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="35" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="270" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="24"/>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{732F3307-74D6-42E3-9137-0094B227B39E}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1079,43 +1005,43 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P1" s="6" t="s">
         <v>4</v>
@@ -1126,9 +1052,9 @@
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
       <c r="E2" s="9"/>
       <c r="F2" s="10"/>
       <c r="G2" s="9"/>
@@ -1139,8 +1065,8 @@
       <c r="L2" s="10"/>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
       <c r="Q2" s="11">
         <f>SUM(C2:P2)</f>
         <v>0</v>
@@ -1148,9 +1074,9 @@
     </row>
     <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
       <c r="E3" s="13"/>
       <c r="F3" s="14"/>
       <c r="G3" s="13"/>
@@ -1161,8 +1087,8 @@
       <c r="L3" s="14"/>
       <c r="M3" s="13"/>
       <c r="N3" s="14"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
       <c r="Q3" s="15">
         <f t="shared" ref="Q3:Q11" si="0">SUM(C3:P3)</f>
         <v>0</v>
@@ -1170,9 +1096,9 @@
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
       <c r="E4" s="13"/>
       <c r="F4" s="14"/>
       <c r="G4" s="13"/>
@@ -1183,8 +1109,8 @@
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
       <c r="Q4" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1192,9 +1118,9 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
@@ -1204,9 +1130,9 @@
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
       <c r="Q5" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1214,9 +1140,9 @@
     </row>
     <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -1227,8 +1153,8 @@
       <c r="L6" s="14"/>
       <c r="M6" s="13"/>
       <c r="N6" s="13"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1236,9 +1162,9 @@
     </row>
     <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
@@ -1249,8 +1175,8 @@
       <c r="L7" s="13"/>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
       <c r="Q7" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1258,9 +1184,9 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
@@ -1271,8 +1197,8 @@
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
       <c r="Q8" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1280,9 +1206,9 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
@@ -1293,8 +1219,8 @@
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
       <c r="Q9" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1302,9 +1228,9 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -1315,8 +1241,8 @@
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
       <c r="Q10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1324,9 +1250,9 @@
     </row>
     <row r="11" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
@@ -1337,8 +1263,8 @@
       <c r="L11" s="13"/>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
       <c r="Q11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
